--- a/product_selector_out/STM32H7A3-7B3.xlsx
+++ b/product_selector_out/STM32H7A3-7B3.xlsx
@@ -1338,7 +1338,7 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7b3ri.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7b3ri.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7b3ri.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7b3ri.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7b3ri.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="BO27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7b3ri.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="BO28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="BO29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="BO30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="BO31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="BO32" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7b3ri.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8415,7 @@
       </c>
       <c r="BO33" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="BO34" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ai.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
@@ -9960,9 +9960,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AY13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr">
@@ -11645,9 +11645,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AY18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -12319,9 +12319,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AY20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -12993,9 +12993,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AY22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -14341,9 +14341,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AY26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ26" s="6" t="inlineStr">
@@ -14678,9 +14678,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AY27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ27" s="6" t="inlineStr">
@@ -16363,9 +16363,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AY32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ32" s="6" t="inlineStr">
@@ -17138,7 +17138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17297,19 +17297,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32H7B3NI</t>
+          <t>STM32H7A3IG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 41. Typical current consumption RAM shutoff in Stop mode, added</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -17353,7 +17353,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -17363,19 +17363,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32H7A3IG</t>
+          <t>STM32H7A3RI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -17397,7 +17397,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -17429,19 +17429,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32H7A3RI</t>
+          <t>STM32H7A3RG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -17463,7 +17463,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -17495,19 +17495,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32H7A3RG</t>
+          <t>STM32H7B3AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -17529,7 +17529,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -17551,7 +17551,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -17561,7 +17561,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -17583,19 +17583,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 41. Typical current consumption RAM shutoff in Stop mode, added</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32H7B3AI</t>
+          <t>STM32H7B3II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -17605,7 +17605,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 41. Typical current consumption RAM shutoff in Stop mode, added</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -17639,7 +17639,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -17649,19 +17649,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32H7B3II</t>
+          <t>STM32H7A3ZG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -17671,19 +17671,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32H7B3II</t>
+          <t>STM32H7A3ZG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -17693,7 +17693,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 41. Typical current consumption RAM shutoff in Stop mode, added</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -17705,7 +17705,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -17715,19 +17715,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32H7A3ZG</t>
+          <t>STM32H7B3QI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -17744,12 +17744,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32H7A3ZG</t>
+          <t>STM32H7B3QI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -17771,7 +17771,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -17781,19 +17781,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32H7B3QI</t>
+          <t>STM32H7A3II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -17810,12 +17810,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32H7B3QI</t>
+          <t>STM32H7A3II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -17825,19 +17825,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32H7B3QI</t>
+          <t>STM32H7A3II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -17847,14 +17847,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 41. Typical current consumption RAM shutoff in Stop mode, added</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32H7A3II</t>
+          <t>STM32H7B3VI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -17876,7 +17876,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32H7A3II</t>
+          <t>STM32H7B3VI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -17898,7 +17898,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32H7A3II</t>
+          <t>STM32H7B3VI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -17913,14 +17913,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32H7B3VI</t>
+          <t>STM32H7A3NG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -17942,7 +17942,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32H7B3VI</t>
+          <t>STM32H7A3NG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -17964,7 +17964,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32H7B3VI</t>
+          <t>STM32H7A3NG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -17986,12 +17986,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32H7B3VI</t>
+          <t>STM32H7A3ZI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -18001,19 +18001,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 41. Typical current consumption RAM shutoff in Stop mode, added</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32H7A3NG</t>
+          <t>STM32H7A3ZI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -18030,12 +18030,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32H7A3NG</t>
+          <t>STM32H7A3ZI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -18045,19 +18045,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32H7A3NG</t>
+          <t>STM32H7A3AG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -18067,19 +18067,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32H7A3ZI</t>
+          <t>STM32H7A3AG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -18096,12 +18096,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32H7A3ZI</t>
+          <t>STM32H7A3AG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -18111,19 +18111,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32H7A3ZI</t>
+          <t>STM32H7B3ZI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -18133,19 +18133,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32H7A3AG</t>
+          <t>STM32H7B3ZI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -18162,12 +18162,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32H7A3AG</t>
+          <t>STM32H7B3ZI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -18177,19 +18177,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32H7A3AG</t>
+          <t>STM32H7B3RI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -18199,19 +18199,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32H7B3ZI</t>
+          <t>STM32H7B3RI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -18228,12 +18228,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32H7B3ZI</t>
+          <t>STM32H7B3RI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -18243,19 +18243,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32H7B3ZI</t>
+          <t>STM32H7A3VI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -18265,19 +18265,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32H7B3ZI</t>
+          <t>STM32H7A3VI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -18287,19 +18287,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 41. Typical current consumption RAM shutoff in Stop mode, added</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32H7B3RI</t>
+          <t>STM32H7A3VI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -18309,19 +18309,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32H7B3RI</t>
+          <t>STM32H7A3VG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -18338,12 +18338,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32H7B3RI</t>
+          <t>STM32H7A3VG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -18353,19 +18353,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32H7B3RI</t>
+          <t>STM32H7A3VG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -18375,14 +18375,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 41. Typical current consumption RAM shutoff in Stop mode, added</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32H7A3VI</t>
+          <t>STM32H7A3AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -18404,7 +18404,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32H7A3VI</t>
+          <t>STM32H7A3AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -18426,7 +18426,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32H7A3VI</t>
+          <t>STM32H7A3AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -18448,7 +18448,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32H7A3VG</t>
+          <t>STM32H7A3NI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -18470,7 +18470,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32H7A3VG</t>
+          <t>STM32H7A3NI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -18492,7 +18492,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32H7A3VG</t>
+          <t>STM32H7A3NI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -18514,7 +18514,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32H7A3AI</t>
+          <t>STM32H7B3LI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -18536,7 +18536,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32H7A3AI</t>
+          <t>STM32H7B3LI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -18558,7 +18558,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32H7A3AI</t>
+          <t>STM32H7B3LI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -18573,14 +18573,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32H7A3NI</t>
+          <t>STM32H7A3LI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -18602,7 +18602,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32H7A3NI</t>
+          <t>STM32H7A3LI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -18624,7 +18624,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32H7A3NI</t>
+          <t>STM32H7A3LI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -18646,7 +18646,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32H7B3LI</t>
+          <t>STM32H7A3LG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -18668,7 +18668,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32H7B3LI</t>
+          <t>STM32H7A3LG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -18690,7 +18690,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32H7B3LI</t>
+          <t>STM32H7A3LG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -18704,160 +18704,6 @@
         </is>
       </c>
       <c r="D71" t="inlineStr">
-        <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>STM32H7B3LI</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Table 41. Typical current consumption RAM shutoff in Stop mode, added</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>STM32H7A3LI</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>STM32H7A3LI</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>STM32H7A3LI</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>STM32H7A3LG</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>STM32H7A3LG</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>STM32H7A3LG</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
         <is>
           <t>Table 22. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32H7A3-7B3.xlsx
+++ b/product_selector_out/STM32H7A3-7B3.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO34"/>
+  <dimension ref="A1:BP34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.96484375" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1004,6 +1010,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1338,6 +1345,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -1675,6 +1687,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
@@ -2012,6 +2029,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -2349,6 +2371,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -2686,6 +2713,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -3023,6 +3055,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b3ai.pdf</t>
         </is>
       </c>
@@ -3360,6 +3397,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
@@ -3697,6 +3739,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -4034,6 +4081,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
@@ -4371,6 +4423,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -4708,6 +4765,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
@@ -5045,6 +5107,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -5382,6 +5449,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -5719,6 +5791,11 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -6056,6 +6133,11 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
@@ -6393,6 +6475,11 @@
       </c>
       <c r="BO27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
@@ -6730,6 +6817,11 @@
       </c>
       <c r="BO28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -7067,6 +7159,11 @@
       </c>
       <c r="BO29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -7404,6 +7501,11 @@
       </c>
       <c r="BO30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -7741,6 +7843,11 @@
       </c>
       <c r="BO31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -8078,6 +8185,11 @@
       </c>
       <c r="BO32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7b0ab.pdf</t>
         </is>
       </c>
@@ -8415,6 +8527,11 @@
       </c>
       <c r="BO33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
@@ -8752,12 +8869,17 @@
       </c>
       <c r="BO34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7a3ag.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -8780,12 +8902,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -8800,9 +8924,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -8861,7 +8984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO34"/>
+  <dimension ref="A1:BP34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8931,6 +9054,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9274,6 +9398,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -9371,6 +9500,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -9703,7 +9833,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10040,7 +10175,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10377,7 +10517,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10714,7 +10859,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11051,7 +11201,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11388,7 +11543,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11725,7 +11885,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12062,7 +12227,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12399,7 +12569,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12736,7 +12911,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13073,7 +13253,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13410,7 +13595,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13747,7 +13937,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14084,7 +14279,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14421,7 +14621,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
+      <c r="BO26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14758,7 +14963,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO27" s="6" t="inlineStr">
+      <c r="BO27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15095,7 +15305,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO28" s="6" t="inlineStr">
+      <c r="BO28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15432,7 +15647,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO29" s="6" t="inlineStr">
+      <c r="BO29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15769,7 +15989,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO30" s="6" t="inlineStr">
+      <c r="BO30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16106,7 +16331,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO31" s="6" t="inlineStr">
+      <c r="BO31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16443,7 +16673,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO32" s="6" t="inlineStr">
+      <c r="BO32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16780,7 +17015,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO33" s="6" t="inlineStr">
+      <c r="BO33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17117,7 +17357,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO34" s="6" t="inlineStr">
+      <c r="BO34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17125,8 +17370,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
